--- a/data/questionsTest/QuestionTest.xlsx
+++ b/data/questionsTest/QuestionTest.xlsx
@@ -504,9 +504,21 @@
           <t>76804754 : 84.77242588996887 - 6940499 : 84.77242588996887</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>L'évènement de PROVALP 3D à Nice dure **3 heures**.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>76804754</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>[{'id': 76804754, 'text': "&lt;h1&gt;Description de l'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L'évènement se déroule à l'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l'évènement durera : 0 days 03:00:00&lt;/p&gt;", 'metadata': "[{ motsCles : ['1 jeune  1 solution' 'Recrutement']},{ accessibilite : none},{ coordonnees : {'lon': 7.262505, 'lat': 43.714504}},{ telephone : none},{ site_web : none}]", 'model': 'mistral-embed', 'rowHash': '51501cc970790e7fba85ecdae63bc596'}]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -537,9 +549,21 @@
           <t>94917451-6 : none - 78337946 : none</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aucun événement ne s'est produit le 25 août 2025 à Nice selon le contexte fourni.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -570,9 +594,21 @@
           <t>76804754 : 86.70159578323364 - 6940499 : 86.70159578323364</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>L'évènement de recrutement de PROVALP 3D se déroule le **3 septembre 2025 à 9h00** à l'agence Nice Nord. Il est conseillé de prévoir la matinée et de se présenter avec un CV.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>76804754</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[{'id': 76804754, 'text': "&lt;h1&gt;Description de l'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L'évènement se déroule à l'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l'évènement durera : 0 days 03:00:00&lt;/p&gt;", 'metadata': "[{ motsCles : ['1 jeune  1 solution' 'Recrutement']},{ accessibilite : none},{ coordonnees : {'lon': 7.262505, 'lat': 43.714504}},{ telephone : none},{ site_web : none}]", 'model': 'mistral-embed', 'rowHash': '51501cc970790e7fba85ecdae63bc596'}]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -603,9 +639,21 @@
           <t>21312701 : 81.92882537841797</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Aucun évènement ne s'est déroulé au Lycée Parc Impérial à Nice en 2025 selon le contexte fourni.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/questionsTest/QuestionTest.xlsx
+++ b/data/questionsTest/QuestionTest.xlsx
@@ -506,17 +506,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>L'évènement de PROVALP 3D à Nice dure **3 heures**.</t>
+          <t>L'événement de PROVALP 3D à Nice dure **3 heures**.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>76804754</t>
+          <t>76804754,6940499</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[{'id': 76804754, 'text': "&lt;h1&gt;Description de l'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L'évènement se déroule à l'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l'évènement durera : 0 days 03:00:00&lt;/p&gt;", 'metadata': "[{ motsCles : ['1 jeune  1 solution' 'Recrutement']},{ accessibilite : none},{ coordonnees : {'lon': 7.262505, 'lat': 43.714504}},{ telephone : none},{ site_web : none}]", 'model': 'mistral-embed', 'rowHash': '51501cc970790e7fba85ecdae63bc596'}]</t>
+          <t>[{'id': 76804754, 'text': "&lt;h1&gt;Description de l'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L'évènement se déroule à l'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l'évènement durera : 0 days 03:00:00&lt;/p&gt;", 'metadata': "[{ motsCles : ['1 jeune  1 solution' 'Recrutement']},{ accessibilite : none},{ coordonnees : {'lon': 7.262505, 'lat': 43.714504}},{ telephone : none},{ site_web : none}]", 'model': 'mistral-embed', 'rowHash': '51501cc970790e7fba85ecdae63bc596'}, {'id': 6940499, 'text': "&lt;h1&gt;Description de l'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L'évènement se déroule à l'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l'évènement durera : 0 days 03:00:00&lt;/p&gt;", 'metadata': "[{ motsCles : ['Job dating' '1 jeune  1 solution' 'Recrutement' 'Tout public' 'CDI'\n 'en physique']},{ accessibilite : none},{ coordonnees : {'lon': 7.262505, 'lat': 43.714504}},{ telephone : none},{ site_web : none}]", 'model': 'mistral-embed', 'rowHash': '0b7e60eea3635675753ea6e8821be9cc'}]</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>L'évènement de recrutement de PROVALP 3D se déroule le **3 septembre 2025 à 9h00** à l'agence Nice Nord. Il est conseillé de prévoir la matinée et de se présenter avec un CV.</t>
+          <t>L'évènement de recrutement de PROVALP 3D se déroule le **3 septembre 2025 à 9h00** à l'Agence Nice Nord (06100 Nice). Il est conseillé de prévoir la matinée.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>76804754</t>
+          <t>76804754,6940499</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[{'id': 76804754, 'text': "&lt;h1&gt;Description de l'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L'évènement se déroule à l'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l'évènement durera : 0 days 03:00:00&lt;/p&gt;", 'metadata': "[{ motsCles : ['1 jeune  1 solution' 'Recrutement']},{ accessibilite : none},{ coordonnees : {'lon': 7.262505, 'lat': 43.714504}},{ telephone : none},{ site_web : none}]", 'model': 'mistral-embed', 'rowHash': '51501cc970790e7fba85ecdae63bc596'}]</t>
+          <t>[{'id': 76804754, 'text': "&lt;h1&gt;Description de l'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L'évènement se déroule à l'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l'évènement durera : 0 days 03:00:00&lt;/p&gt;", 'metadata': "[{ motsCles : ['1 jeune  1 solution' 'Recrutement']},{ accessibilite : none},{ coordonnees : {'lon': 7.262505, 'lat': 43.714504}},{ telephone : none},{ site_web : none}]", 'model': 'mistral-embed', 'rowHash': '51501cc970790e7fba85ecdae63bc596'}, {'id': 6940499, 'text': "&lt;h1&gt;Description de l'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L'évènement se déroule à l'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l'évènement durera : 0 days 03:00:00&lt;/p&gt;", 'metadata': "[{ motsCles : ['Job dating' '1 jeune  1 solution' 'Recrutement' 'Tout public' 'CDI'\n 'en physique']},{ accessibilite : none},{ coordonnees : {'lon': 7.262505, 'lat': 43.714504}},{ telephone : none},{ site_web : none}]", 'model': 'mistral-embed', 'rowHash': '0b7e60eea3635675753ea6e8821be9cc'}]</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21312701 : 148</t>
+          <t>21312701 : none</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21312701 : 81.92882537841797</t>
+          <t>21312701 : none</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/data/questionsTest/QuestionTest.xlsx
+++ b/data/questionsTest/QuestionTest.xlsx
@@ -481,42 +481,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Combien de temps dure l'évènement de PROVALP 3D à Nice ?</t>
+          <t>quel évènement se sont produit le 25 août 2025 à Nice ?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>L'évènement de recrutement de PROVALP 3D à Nice dure 3 heures (de 9h00 à 12h00 environ).</t>
+          <t>2 évènements se sont déroulé le 25 aout 2025 à Nice, le premier : comment mobiliser vos applications France Travail, le deuxième : atelier le héros aux mille et un visage avec Dany Albiach</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>76804754 - 6940499</t>
+          <t>94917451-6 - 78337946</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>76804754 : 1 - 6940499 : 2</t>
+          <t>94917451-6 : none - 78337946 : none</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76804754 : 84.77242588996887 - 6940499 : 84.77242588996887</t>
+          <t>94917451-6 : none - 78337946 : none</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>L'événement de PROVALP 3D à Nice dure **3 heures**.</t>
+          <t>Aucun événement ne s'est produit le 25 août 2025 à Nice selon le contexte fourni.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>76804754,6940499</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[{'id': 76804754, 'text': "&lt;h1&gt;Description de l'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L'évènement se déroule à l'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l'évènement durera : 0 days 03:00:00&lt;/p&gt;", 'metadata': "[{ motsCles : ['1 jeune  1 solution' 'Recrutement']},{ accessibilite : none},{ coordonnees : {'lon': 7.262505, 'lat': 43.714504}},{ telephone : none},{ site_web : none}]", 'model': 'mistral-embed', 'rowHash': '51501cc970790e7fba85ecdae63bc596'}, {'id': 6940499, 'text': "&lt;h1&gt;Description de l'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L'évènement se déroule à l'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l'évènement durera : 0 days 03:00:00&lt;/p&gt;", 'metadata': "[{ motsCles : ['Job dating' '1 jeune  1 solution' 'Recrutement' 'Tout public' 'CDI'\n 'en physique']},{ accessibilite : none},{ coordonnees : {'lon': 7.262505, 'lat': 43.714504}},{ telephone : none},{ site_web : none}]", 'model': 'mistral-embed', 'rowHash': '0b7e60eea3635675753ea6e8821be9cc'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -526,42 +526,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>quel évènement se sont produit le 25 août 2025 à Nice ?</t>
+          <t>Combien de temps dure l'évènement de PROVALP 3D à Nice ?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2 évènements se sont déroulé le 25 aout 2025 à Nice, le premier : comment mobiliser vos applications France Travail, le deuxième : atelier le héros aux mille et un visage avec Dany Albiach</t>
+          <t>L'évènement de recrutement de PROVALP 3D à Nice dure 3 heures (de 9h00 à 12h00 environ).</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>94917451-6 - 78337946</t>
+          <t>76804754 - 6940499</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>94917451-6 : none - 78337946 : none</t>
+          <t>76804754 : 1 - 6940499 : 2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>94917451-6 : none - 78337946 : none</t>
+          <t>76804754 : 84.77242588996887 - 6940499 : 84.77242588996887</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aucun événement ne s'est produit le 25 août 2025 à Nice selon le contexte fourni.</t>
+          <t>L'événement de PROVALP 3D à Nice dure **3 heures**.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>76804754,6940499</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'id': 76804754, 'text': "&lt;h1&gt;Description de l'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L'évènement se déroule à l'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l'évènement durera : 0 days 03:00:00&lt;/p&gt;", 'metadata': "[{ motsCles : ['1 jeune  1 solution' 'Recrutement']},{ accessibilite : none},{ coordonnees : {'lon': 7.262505, 'lat': 43.714504}},{ telephone : none},{ site_web : none}]", 'model': 'mistral-embed', 'rowHash': '51501cc970790e7fba85ecdae63bc596'}, {'id': 6940499, 'text': "&lt;h1&gt;Description de l'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L'évènement se déroule à l'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l'évènement durera : 0 days 03:00:00&lt;/p&gt;", 'metadata': "[{ motsCles : ['Job dating' '1 jeune  1 solution' 'Recrutement' 'Tout public' 'CDI'\n 'en physique']},{ accessibilite : none},{ coordonnees : {'lon': 7.262505, 'lat': 43.714504}},{ telephone : none},{ site_web : none}]", 'model': 'mistral-embed', 'rowHash': '0b7e60eea3635675753ea6e8821be9cc'}]</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>L'évènement de recrutement de PROVALP 3D se déroule le **3 septembre 2025 à 9h00** à l'Agence Nice Nord (06100 Nice). Il est conseillé de prévoir la matinée.</t>
+          <t>L'évènement de recrutement de PROVALP 3D se déroule le **3 septembre 2025 à 9h00** à l'Agence NICE NORD, 06100 Nice. Il est conseillé de prévoir la matinée.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -631,27 +631,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21312701 : none</t>
+          <t>21312701 : 148</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21312701 : none</t>
+          <t>21312701 : 81.92882537841797</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aucun évènement ne s'est déroulé au Lycée Parc Impérial à Nice en 2025 selon le contexte fourni.</t>
+          <t>La conférence « Terre &amp; Ciel » destinée à faire découvrir les métiers du secteur aérien ainsi que de l’industrie aéronautique et spatiale s'est déroulée au Lycée Parc Impérial le 26 novembre 2025.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>21312701</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'id': 21312701, 'text': "&lt;h1&gt;Description de l'évènement : &lt;/h1&gt;&lt;p&gt;La conférence « Terre &amp;amp; Ciel » est destinée à une trentaine de vos élèves et est entièrement prise en charge par notre association Aérométiers. Elle vise à faire découvrir les métiers du secteur aérien ainsi que de l’industrie aéronautique et spatiale, durant 2 heures. Cette conférence interactive permet aux jeunes de réfléchir à leur orientation professionnelle.&lt;br&gt;Pour garantir le bon déroulement de la conférence, certaines conditions doivent être respectées :&lt;/p&gt;\n&lt;ul&gt;\n&lt;li&gt;1. 15 élèves minimum - 30 élèves maximum&lt;/li&gt;\n&lt;li&gt;2. Un format de 2 heures&lt;/li&gt;\n&lt;li&gt;3. Une salle dédiée&lt;/li&gt;\n&lt;li&gt;4. La présence d'un membre de l'équipe éducative&lt;/li&gt;\n&lt;li&gt;5. Un tableau, un PC équipé d'un rétroprojecteur et d'enceintes pour visionner un PowerPoint et des vidéos.&lt;/li&gt;\n&lt;/ul&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L'évènement se déroule à l'adresse suivante : Lycée Parc Impérial, 2 avenue paul arène&lt;br&gt;- L'évènement aura lieu à la date suivante : 26-November-2025 08:00:00&lt;br&gt;- l'évènement durera : 0 days 02:00:00&lt;/p&gt;", 'metadata': "[{ motsCles : none},{ accessibilite : none},{ coordonnees : {'lon': 7.251804, 'lat': 43.708985}},{ telephone : none},{ site_web : none}]", 'model': 'mistral-embed', 'rowHash': 'f27d139e712c9c321daa4b4c350e3ba5'}]</t>
         </is>
       </c>
     </row>
